--- a/public/crawlability-midot-september-2026.xlsx
+++ b/public/crawlability-midot-september-2026.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של midot ב-SE Ranking (הסריקה האחרונה: 2025-01-28).</t>
+          <t>להריץ מחדש את ה-Website Audit של midot ב-SE Ranking (הסריקה האחרונה: 2025-01-28); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-midot-september-2026.xlsx
+++ b/public/crawlability-midot-september-2026.xlsx
@@ -41,7 +41,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,11 +51,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3A5F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -76,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -85,9 +80,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -489,12 +481,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>גבוהה</t>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): כתובת אחת (הבולטת: https://midot.co.il/wp-content/themes/midot-th/css-heb/cstyle-blog-rtl.css?ver=3, 0 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): כתובת אחת (הבולטת: https://midot.co.il/wp-content/themes/midot-th/css-heb/cstyle-blog-rtl.css?ver=3…, 0 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -502,7 +494,7 @@
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
@@ -517,7 +509,7 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
@@ -613,7 +605,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/wp-content/themes/midot-th/css-heb/cstyle-blog-rtl.css?ver=3.272</t>
         </is>
@@ -633,7 +625,7 @@
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/איך-למנוע-מקרי-גניבה-והונאה-בארגון-דרכ/
 https://midot.co.il/תשאול-מהימנות-ראיון-עבודה/
@@ -659,7 +651,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
@@ -750,7 +742,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/category/integrity-test</t>
         </is>
@@ -763,7 +755,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/category/integrity-test/</t>
         </is>
@@ -774,7 +766,7 @@
       <c r="F2" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/blog/
 https://midot.co.il/tag/פוליגרף/
@@ -795,19 +787,19 @@
           <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/category/integrity-test/</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/category/מבחן-כישורים</t>
         </is>
@@ -820,7 +812,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/category/מבחן-כישורים/</t>
         </is>
@@ -831,7 +823,7 @@
       <c r="F3" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/blog/
 https://midot.co.il/tag/פוליגרף/
@@ -852,19 +844,19 @@
           <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/category/מבחן-כישורים/</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/category/professional-information</t>
         </is>
@@ -877,7 +869,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/category/professional-information/</t>
         </is>
@@ -888,7 +880,7 @@
       <c r="F4" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/blog/
 https://midot.co.il/tag/פוליגרף/
@@ -909,19 +901,19 @@
           <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/category/professional-information/</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/category/polygraph</t>
         </is>
@@ -934,7 +926,7 @@
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/category/polygraph/</t>
         </is>
@@ -945,7 +937,7 @@
       <c r="F5" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/blog/
 https://midot.co.il/tag/פוליגרף/
@@ -966,12 +958,12 @@
           <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/category/polygraph/</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
@@ -1062,7 +1054,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/cdn-cgi/l/email-protection</t>
         </is>
@@ -1082,7 +1074,7 @@
       <c r="F2" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/הצהרת-נגישות/
 https://midot.co.il/צרו-קשר-מידות/
@@ -1099,7 +1091,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>קישורי Cloudflare (ללא טיפול)</t>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -1108,7 +1100,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
@@ -1185,7 +1177,7 @@
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/sitemap_index.xml</t>
         </is>
@@ -1239,7 +1231,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/sitemap_index.xml</t>
         </is>
@@ -1261,7 +1253,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/post-sitemap.xml</t>
         </is>
@@ -1283,7 +1275,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/page-sitemap.xml</t>
         </is>
@@ -1305,7 +1297,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/product-sitemap.xml</t>
         </is>
@@ -1327,7 +1319,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/manager-sitemap.xml</t>
         </is>
@@ -1349,7 +1341,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/test_case-sitemap.xml</t>
         </is>
@@ -1371,7 +1363,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/publication-sitemap.xml</t>
         </is>
@@ -1393,7 +1385,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/landpage-sitemap.xml</t>
         </is>
@@ -1415,7 +1407,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/conference-sitemap.xml</t>
         </is>
@@ -1437,7 +1429,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/single_publication-sitemap.xml</t>
         </is>
@@ -1459,7 +1451,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/category-sitemap.xml</t>
         </is>
@@ -1481,7 +1473,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/post_tag-sitemap.xml</t>
         </is>
@@ -1503,7 +1495,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/sitemap.xml</t>
         </is>
@@ -1525,7 +1517,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/wp-sitemap.xml</t>
         </is>
@@ -1564,7 +1556,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/</t>
         </is>
@@ -1574,7 +1566,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/ (0 הפניות)</t>
         </is>
@@ -1586,7 +1578,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>http://midot.co.il/</t>
         </is>
@@ -1596,7 +1588,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/ (1 הפניות)</t>
         </is>
@@ -1608,7 +1600,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>https://www.midot.co.il/</t>
         </is>
@@ -1618,7 +1610,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/ (1 הפניות)</t>
         </is>
@@ -1630,7 +1622,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>http://www.midot.co.il/</t>
         </is>
@@ -1640,7 +1632,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/ (2 הפניות)</t>
         </is>
@@ -1693,7 +1685,7 @@
           <t>canonical</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>https://midot.co.il/</t>
         </is>

--- a/public/crawlability-midot-september-2026.xlsx
+++ b/public/crawlability-midot-september-2026.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): כתובת אחת (הבולטת: https://midot.co.il/wp-content/themes/midot-th/css-heb/cstyle-blog-rtl.css?ver=3…, 0 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): כתובת אחת (הבולטת: https://midot.co.il/wp-content/themes/midot-th/css-heb/cstyle-blog-rtl.css?ver=3…, 18 עמודי מקור). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-midot-september-2026.xlsx
+++ b/public/crawlability-midot-september-2026.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): כתובת אחת (הבולטת: https://midot.co.il/wp-content/themes/midot-th/css-heb/cstyle-blog-rtl.css?ver=3…, 18 עמודי מקור). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): כתובת אחת; הבולטת https://midot.co.il/wp-content/themes/midot-th/css-heb/cstyle-blog-rtl.css?ver=3… (18 עמודי מקור).</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 4 כתובות (הבולטת: https://midot.co.il/category/integrity-test, 7 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: 4 כתובות; הבולטת https://midot.co.il/category/integrity-test (7 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של midot ב-SE Ranking (הסריקה האחרונה: 2025-01-28); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של midot ב-SE Ranking; הסריקה האחרונה: 2025-01-28.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-midot-september-2026.xlsx
+++ b/public/crawlability-midot-september-2026.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -502,21 +502,6 @@
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>קישורים פנימיים ללא לוכסן סופי: 4 כתובות; הבולטת https://midot.co.il/category/integrity-test (7 קישורים נכנסים).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של midot ב-SE Ranking; הסריקה האחרונה: 2025-01-28.</t>
         </is>
       </c>
     </row>
